--- a/output/pdf_financials_xlsx/VIK.xlsx
+++ b/output/pdf_financials_xlsx/VIK.xlsx
@@ -607,10 +607,10 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>0</v>
+        <v>0.03483</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>0</v>
+        <v>0.324574</v>
       </c>
       <c r="D9" s="3" t="n">
         <v>0</v>
@@ -629,7 +629,7 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.03104</v>
+        <v>0.06587</v>
       </c>
       <c r="C10" s="3" t="n">
         <v>36.783193</v>
@@ -19048,12 +19048,16 @@
           <t>Royalty expenses</t>
         </is>
       </c>
-      <c r="D381" t="inlineStr"/>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E381" s="5" t="n">
-        <v>-0.03483</v>
+        <v>0.03483</v>
       </c>
       <c r="F381" s="5" t="n">
-        <v>-0.324574</v>
+        <v>0.324574</v>
       </c>
       <c r="G381" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/VIK.xlsx
+++ b/output/pdf_financials_xlsx/VIK.xlsx
@@ -629,7 +629,7 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.06587</v>
+        <v>1.462737</v>
       </c>
       <c r="C10" s="3" t="n">
         <v>36.783193</v>
@@ -679,7 +679,7 @@
         <v>0</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.031729</v>
       </c>
       <c r="E12" s="3" t="n">
         <v>0</v>
@@ -1029,7 +1029,7 @@
         <v>-20.377817</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-24.764827</v>
+        <v>-24.796556</v>
       </c>
       <c r="E27" s="3" t="n">
         <v>-14.482638</v>
@@ -1073,7 +1073,7 @@
         <v>-20.145409</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-23.038166</v>
+        <v>-23.069895</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>-14.022935</v>
@@ -1097,7 +1097,7 @@
         <v>-117.9296838412978</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>-418.2148898894492</v>
+        <v>-418.7908706442238</v>
       </c>
       <c r="E30" s="3" t="n">
         <v>-4801.191144649265</v>
@@ -1166,19 +1166,19 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.413337</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>6.56411</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.06657200000000001</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.013852</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.021577</v>
       </c>
     </row>
     <row r="35">
@@ -1210,19 +1210,19 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.413337</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>6.56411</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.06657200000000001</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.013852</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.021577</v>
       </c>
     </row>
     <row r="37">
@@ -1474,19 +1474,19 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>2.187149</v>
+        <v>1.773812</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>9.518387000000001</v>
+        <v>2.954277</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.151365</v>
+        <v>0.08479299999999999</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.057636</v>
+        <v>0.043784</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.057486</v>
+        <v>0.035909</v>
       </c>
     </row>
     <row r="49">
@@ -3202,10 +3202,10 @@
         <v>0</v>
       </c>
       <c r="C124" s="3" t="n">
-        <v>0</v>
+        <v>-0.004</v>
       </c>
       <c r="D124" s="3" t="n">
-        <v>0</v>
+        <v>-0.037919</v>
       </c>
       <c r="E124" s="3" t="n">
         <v>0</v>
@@ -3224,10 +3224,10 @@
         <v>0</v>
       </c>
       <c r="C125" s="3" t="n">
-        <v>0</v>
+        <v>-0.004</v>
       </c>
       <c r="D125" s="3" t="n">
-        <v>0</v>
+        <v>-0.037919</v>
       </c>
       <c r="E125" s="3" t="n">
         <v>0</v>
@@ -3559,7 +3559,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -5226,7 +5226,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -6921,7 +6921,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E82" s="5" t="n">
@@ -11913,7 +11913,11 @@
           <t>Surface lease payments (note 9)</t>
         </is>
       </c>
-      <c r="D206" t="inlineStr"/>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E206" t="inlineStr">
         <is>
           <t>-</t>
@@ -17492,7 +17496,7 @@
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E343" t="inlineStr">
@@ -19737,7 +19741,7 @@
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E398" s="5" t="n">

--- a/output/pdf_financials_xlsx/VIK.xlsx
+++ b/output/pdf_financials_xlsx/VIK.xlsx
@@ -1048,7 +1048,7 @@
         <v>0</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>0.232408</v>
+        <v>0.237098</v>
       </c>
       <c r="D28" s="3" t="n">
         <v>1.726661</v>
@@ -1070,7 +1070,7 @@
         <v>-1.415186</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-20.145409</v>
+        <v>-20.140719</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>-23.069895</v>
@@ -1094,7 +1094,7 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>-117.9296838412978</v>
+        <v>-117.9022289399247</v>
       </c>
       <c r="D30" s="3" t="n">
         <v>-418.7908706442238</v>
@@ -2670,7 +2670,7 @@
         <v>0</v>
       </c>
       <c r="C100" s="3" t="n">
-        <v>0</v>
+        <v>0.237098</v>
       </c>
       <c r="D100" s="3" t="n">
         <v>0</v>
@@ -13098,7 +13098,11 @@
           <t>Depreciation - Property, Plant and Equipment</t>
         </is>
       </c>
-      <c r="D235" t="inlineStr"/>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E235" t="inlineStr">
         <is>
           <t>-</t>
@@ -13139,7 +13143,11 @@
           <t>Depreciation - Right of Use Assets</t>
         </is>
       </c>
-      <c r="D236" t="inlineStr"/>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E236" t="inlineStr">
         <is>
           <t>-</t>
@@ -19337,7 +19345,11 @@
           <t>Depreciation - Property, Plant and Equipment 6</t>
         </is>
       </c>
-      <c r="D388" t="inlineStr"/>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E388" t="inlineStr">
         <is>
           <t>-</t>
@@ -19378,7 +19390,11 @@
           <t>Depreciation – Right-of-Use Assets 8</t>
         </is>
       </c>
-      <c r="D389" t="inlineStr"/>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E389" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/VIK.xlsx
+++ b/output/pdf_financials_xlsx/VIK.xlsx
@@ -1983,16 +1983,16 @@
         <v>0</v>
       </c>
       <c r="C70" s="3" t="n">
-        <v>0</v>
+        <v>0.032897</v>
       </c>
       <c r="D70" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E70" s="3" t="n">
-        <v>0</v>
+        <v>0.021888</v>
       </c>
       <c r="F70" s="3" t="n">
-        <v>0</v>
+        <v>0.01222</v>
       </c>
     </row>
     <row r="71">
@@ -2005,16 +2005,16 @@
         <v>0</v>
       </c>
       <c r="C71" s="3" t="n">
-        <v>0</v>
+        <v>0.032897</v>
       </c>
       <c r="D71" s="3" t="n">
         <v>0.284999</v>
       </c>
       <c r="E71" s="3" t="n">
-        <v>0.313499</v>
+        <v>0.335387</v>
       </c>
       <c r="F71" s="3" t="n">
-        <v>0.344849</v>
+        <v>0.357069</v>
       </c>
     </row>
     <row r="72">
@@ -2093,16 +2093,16 @@
         <v>0.067429</v>
       </c>
       <c r="C75" s="3" t="n">
-        <v>4.865597</v>
+        <v>4.8327</v>
       </c>
       <c r="D75" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E75" s="3" t="n">
-        <v>12.035706</v>
+        <v>12.013818</v>
       </c>
       <c r="F75" s="3" t="n">
-        <v>13.002209</v>
+        <v>12.989989</v>
       </c>
     </row>
     <row r="76">
@@ -2206,10 +2206,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C80" s="3" t="n">
+        <v>0.001018063706395589</v>
       </c>
       <c r="D80" s="1" t="inlineStr">
         <is>
@@ -2887,10 +2885,10 @@
         </is>
       </c>
       <c r="B110" s="3" t="n">
-        <v>0</v>
+        <v>0.110661</v>
       </c>
       <c r="C110" s="3" t="n">
-        <v>0</v>
+        <v>0.492361</v>
       </c>
       <c r="D110" s="3" t="n">
         <v>0</v>
@@ -3932,7 +3930,11 @@
           <t>Lease liabilities (Note 8)</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>-</t>
@@ -5850,7 +5852,11 @@
           <t>Lease liabilities (note 9) 16,186</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr"/>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E57" t="inlineStr">
         <is>
           <t>-</t>
@@ -6276,7 +6282,11 @@
           <t>Lease liabilities (note 9) 80,941</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr"/>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E67" t="inlineStr">
         <is>
           <t>-</t>
@@ -10798,7 +10808,11 @@
           <t>Shares issued for cash</t>
         </is>
       </c>
-      <c r="D179" t="inlineStr"/>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E179" t="inlineStr">
         <is>
           <t>-</t>
@@ -11374,7 +11388,11 @@
           <t>Deferred tax expense (note 18)</t>
         </is>
       </c>
-      <c r="D193" t="inlineStr"/>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E193" t="inlineStr">
         <is>
           <t>-</t>
@@ -11708,7 +11726,11 @@
           <t>Shares issued for cash (note 19)</t>
         </is>
       </c>
-      <c r="D201" t="inlineStr"/>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E201" t="inlineStr">
         <is>
           <t>-</t>
@@ -12856,7 +12878,11 @@
           <t>Accretion Expense</t>
         </is>
       </c>
-      <c r="D229" t="inlineStr"/>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E229" s="5" t="n">
         <v>0.110661</v>
       </c>
@@ -13725,7 +13751,11 @@
           <t>Shares Issued for Cash</t>
         </is>
       </c>
-      <c r="D250" t="inlineStr"/>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E250" s="5" t="n">
         <v>4.292833</v>
       </c>
